--- a/outputs/marine_equipment/Фильтры_и_клинкеты.xlsx
+++ b/outputs/marine_equipment/Фильтры_и_клинкеты.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Фильтры забортной воды" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Клинкеты и задвижки" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Клинкеты (задвижки)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1145,7 +1145,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Клинкеты и задвижки: все, что есть на складе (клинкет и задвижка клинкетная — одно и то же)</t>
+          <t>Клинкеты, они же задвижки клинкетные: все, что есть на складе (клинкет и задвижка клинкетная — одно и то же)</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Клинкеты и задвижки клинкетные</t>
+          <t>Клинкеты (задвижки клинкетные)</t>
         </is>
       </c>
       <c r="B5" s="4" t="n"/>
@@ -2118,7 +2118,7 @@
     <row r="27">
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Итого: клинкеты и задвижки клинкетные</t>
+          <t>Итого: клинкеты (задвижки клинкетные)</t>
         </is>
       </c>
       <c r="F27" s="9">
